--- a/documents/cosco_shipping_rates_sep_2026.xlsx
+++ b/documents/cosco_shipping_rates_sep_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xPrecisco\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{22AD3146-C0CC-46D3-BCE9-744F24573A39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB1CB4B9-D978-4A09-816C-6694CAC9EAA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Intra-Asia Rates" sheetId="5" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="60">
   <si>
     <t>Region / Port</t>
   </si>
@@ -570,8 +570,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="17.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -891,6 +894,61 @@
       </c>
       <c r="F16" t="s">
         <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20">
+        <v>75</v>
+      </c>
+      <c r="C20">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21">
+        <v>175</v>
+      </c>
+      <c r="C21">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22">
+        <v>200</v>
+      </c>
+      <c r="C22">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23">
+        <v>100</v>
+      </c>
+      <c r="C23">
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -900,7 +958,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1121,6 +1179,61 @@
       </c>
       <c r="F11" t="s">
         <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19">
+        <v>75</v>
+      </c>
+      <c r="C19">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20">
+        <v>175</v>
+      </c>
+      <c r="C20">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21">
+        <v>200</v>
+      </c>
+      <c r="C21">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22">
+        <v>100</v>
+      </c>
+      <c r="C22">
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -1130,7 +1243,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1250,6 +1363,61 @@
       </c>
       <c r="E7" t="s">
         <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11">
+        <v>75</v>
+      </c>
+      <c r="C11">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12">
+        <v>175</v>
+      </c>
+      <c r="C12">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13">
+        <v>200</v>
+      </c>
+      <c r="C13">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14">
+        <v>100</v>
+      </c>
+      <c r="C14">
+        <v>130</v>
       </c>
     </row>
   </sheetData>
